--- a/docs/validation/V10_Channel_Story_National_Counterpart.xlsx
+++ b/docs/validation/V10_Channel_Story_National_Counterpart.xlsx
@@ -652,7 +652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F137"/>
+  <dimension ref="A1:F138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -677,10 +677,10 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="18" customHeight="1">
+    <row r="3" ht="16" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Check 10 of 17 · Model pass · Recorded in document 22 · Gates G4, G5, G7</t>
+          <t>Check 10 of 17 · Model pass · Recorded in document 22 · Gates G4, G5, G7, G8</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>G4, G5 and G7</t>
+          <t>G4, G5, G7 and G8</t>
         </is>
       </c>
       <c r="D15" s="7" t="n"/>
@@ -1721,114 +1721,117 @@
       <c r="E105" s="7" t="n"/>
       <c r="F105" s="8" t="n"/>
     </row>
-    <row r="106" ht="8" customHeight="1"/>
-    <row r="107" ht="22" customHeight="1">
-      <c r="A107" s="5" t="inlineStr">
+    <row r="106" ht="16" customHeight="1">
+      <c r="B106" s="10" t="inlineStr">
+        <is>
+          <t>G8.01</t>
+        </is>
+      </c>
+      <c r="C106" s="10" t="inlineStr">
+        <is>
+          <t>R1 report pass</t>
+        </is>
+      </c>
+      <c r="D106" s="7" t="n"/>
+      <c r="E106" s="7" t="n"/>
+      <c r="F106" s="8" t="n"/>
+    </row>
+    <row r="107" ht="8" customHeight="1"/>
+    <row r="108" ht="22" customHeight="1">
+      <c r="A108" s="5" t="inlineStr">
         <is>
           <t>7. IF IT FAILS</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="20" customHeight="1">
-      <c r="B108" s="13" t="inlineStr">
+    <row r="109" ht="20" customHeight="1">
+      <c r="B109" s="13" t="inlineStr">
         <is>
           <t>7.1 What usually causes it</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="20" customHeight="1">
-      <c r="B109" s="6" t="inlineStr">
+    <row r="110" ht="20" customHeight="1">
+      <c r="B110" s="6" t="inlineStr">
         <is>
           <t>What you see</t>
         </is>
       </c>
-      <c r="C109" s="6" t="inlineStr">
+      <c r="C110" s="6" t="inlineStr">
         <is>
           <t>Likely cause</t>
         </is>
       </c>
-      <c r="D109" s="8" t="n"/>
-      <c r="E109" s="6" t="inlineStr">
+      <c r="D110" s="8" t="n"/>
+      <c r="E110" s="6" t="inlineStr">
         <is>
           <t>What to do</t>
         </is>
       </c>
-      <c r="F109" s="8" t="n"/>
-    </row>
-    <row r="110" ht="28" customHeight="1">
-      <c r="B110" s="10" t="inlineStr">
+      <c r="F110" s="8" t="n"/>
+    </row>
+    <row r="111" ht="28" customHeight="1">
+      <c r="B111" s="10" t="inlineStr">
         <is>
           <t>All three columns blank</t>
         </is>
       </c>
-      <c r="C110" s="10" t="inlineStr">
+      <c r="C111" s="10" t="inlineStr">
         <is>
           <t>Years outside the loaded range, or measures not built</t>
         </is>
       </c>
-      <c r="D110" s="8" t="n"/>
-      <c r="E110" s="10" t="inlineStr">
+      <c r="D111" s="8" t="n"/>
+      <c r="E111" s="10" t="inlineStr">
         <is>
           <t>Check the loaded range (V02) and the folder build</t>
         </is>
       </c>
-      <c r="F110" s="8" t="n"/>
-    </row>
-    <row r="111" ht="28" customHeight="1">
-      <c r="B111" s="12" t="inlineStr">
+      <c r="F111" s="8" t="n"/>
+    </row>
+    <row r="112" ht="28" customHeight="1">
+      <c r="B112" s="12" t="inlineStr">
         <is>
           <t>Series move differently</t>
         </is>
       </c>
-      <c r="C111" s="12" t="inlineStr">
+      <c r="C112" s="12" t="inlineStr">
         <is>
           <t>A real finding, not an error</t>
         </is>
       </c>
-      <c r="D111" s="8" t="n"/>
-      <c r="E111" s="12" t="inlineStr">
+      <c r="D112" s="8" t="n"/>
+      <c r="E112" s="12" t="inlineStr">
         <is>
           <t>Reword R1 Page 3 per document 01 §8 and record the decision</t>
         </is>
       </c>
-      <c r="F111" s="8" t="n"/>
-    </row>
-    <row r="112" ht="20" customHeight="1">
-      <c r="B112" s="13" t="inlineStr">
+      <c r="F112" s="8" t="n"/>
+    </row>
+    <row r="113" ht="20" customHeight="1">
+      <c r="B113" s="13" t="inlineStr">
         <is>
           <t>7.2 Record the failure</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="29" customHeight="1">
-      <c r="A113" s="16" t="n">
+    <row r="114" ht="29" customHeight="1">
+      <c r="A114" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="B113" s="14" t="inlineStr">
+      <c r="B114" s="14" t="inlineStr">
         <is>
           <t>On the Check Results tab of document 22, set Result to Fail for check 10. Write the numbers you saw in Observed value. Do not change it to N/A and do not clear it.</t>
         </is>
       </c>
     </row>
-    <row r="114" ht="16" customHeight="1">
-      <c r="A114" s="16" t="n">
+    <row r="115" ht="16" customHeight="1">
+      <c r="A115" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="B114" s="14" t="inlineStr">
+      <c r="B115" s="14" t="inlineStr">
         <is>
           <t>Select the Failure Log tab and fill the first empty row:</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="16" customHeight="1">
-      <c r="B115" s="19" t="inlineStr">
-        <is>
-          <t>◦</t>
-        </is>
-      </c>
-      <c r="C115" s="14" t="inlineStr">
-        <is>
-          <t>Failure ID: the next number — F-001, then F-002 and so on.</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1843,7 @@
       </c>
       <c r="C116" s="14" t="inlineStr">
         <is>
-          <t>Run ID and Check #: this run and check number.</t>
+          <t>Failure ID: the next number — F-001, then F-002 and so on.</t>
         </is>
       </c>
     </row>
@@ -1852,7 +1855,7 @@
       </c>
       <c r="C117" s="14" t="inlineStr">
         <is>
-          <t>What was observed: the same numbers.</t>
+          <t>Run ID and Check #: this run and check number.</t>
         </is>
       </c>
     </row>
@@ -1864,57 +1867,57 @@
       </c>
       <c r="C118" s="14" t="inlineStr">
         <is>
+          <t>What was observed: the same numbers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="16" customHeight="1">
+      <c r="B119" s="19" t="inlineStr">
+        <is>
+          <t>◦</t>
+        </is>
+      </c>
+      <c r="C119" s="14" t="inlineStr">
+        <is>
           <t>Root cause: what you found, or ‘not yet known’.</t>
         </is>
       </c>
     </row>
-    <row r="119" ht="16" customHeight="1">
-      <c r="A119" s="16" t="n">
+    <row r="120" ht="16" customHeight="1">
+      <c r="A120" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="B119" s="14" t="inlineStr">
+      <c r="B120" s="14" t="inlineStr">
         <is>
           <t>Fix the cause. Then fill Fix applied, Fixed by and Date fixed. Status changes by itself to ‘Fix applied — not re-verified’.</t>
         </is>
       </c>
     </row>
-    <row r="120" ht="29" customHeight="1">
-      <c r="A120" s="16" t="n">
+    <row r="121" ht="29" customHeight="1">
+      <c r="A121" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="B120" s="14" t="inlineStr">
+      <c r="B121" s="14" t="inlineStr">
         <is>
           <t>Run the whole procedure again as a new run — on Run Summary add Run 2 with Trigger Ad hoc and name the fix in Notes. Record the new result against Run 2.</t>
         </is>
       </c>
     </row>
-    <row r="121" ht="16" customHeight="1">
-      <c r="A121" s="16" t="n">
+    <row r="122" ht="16" customHeight="1">
+      <c r="A122" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="B121" s="14" t="inlineStr">
+      <c r="B122" s="14" t="inlineStr">
         <is>
           <t>When it passes, type Run 2 in Re-verified in run on the Failure Log. Status changes to ‘Closed — re-verified’.</t>
         </is>
       </c>
     </row>
-    <row r="122" ht="8" customHeight="1"/>
-    <row r="123" ht="22" customHeight="1">
-      <c r="A123" s="5" t="inlineStr">
+    <row r="123" ht="8" customHeight="1"/>
+    <row r="124" ht="22" customHeight="1">
+      <c r="A124" s="5" t="inlineStr">
         <is>
           <t>8. WHEN TO RUN IT AGAIN</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="16" customHeight="1">
-      <c r="A124" s="15" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B124" s="14" t="inlineStr">
-        <is>
-          <t>At the model pass.</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1929,7 @@
       </c>
       <c r="B125" s="14" t="inlineStr">
         <is>
-          <t>When R1 Page 3’s text is edited.</t>
+          <t>At the model pass.</t>
         </is>
       </c>
     </row>
@@ -1938,27 +1941,27 @@
       </c>
       <c r="B126" s="14" t="inlineStr">
         <is>
+          <t>When R1 Page 3’s text is edited.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="16" customHeight="1">
+      <c r="A127" s="15" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B127" s="14" t="inlineStr">
+        <is>
           <t>After a reload that revises 2020 data.</t>
         </is>
       </c>
     </row>
-    <row r="127" ht="8" customHeight="1"/>
-    <row r="128" ht="22" customHeight="1">
-      <c r="A128" s="5" t="inlineStr">
+    <row r="128" ht="8" customHeight="1"/>
+    <row r="129" ht="22" customHeight="1">
+      <c r="A129" s="5" t="inlineStr">
         <is>
           <t>9. REFERENCES</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="16" customHeight="1">
-      <c r="A129" s="15" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B129" s="14" t="inlineStr">
-        <is>
-          <t>Document 02 §9 — the seventeen checks and their pass criteria.</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1973,7 @@
       </c>
       <c r="B130" s="14" t="inlineStr">
         <is>
-          <t>Document 22, Check Catalog tab — what this check protects against and where it runs.</t>
+          <t>Document 02 §9 — the seventeen checks and their pass criteria.</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1985,7 @@
       </c>
       <c r="B131" s="14" t="inlineStr">
         <is>
-          <t>Document 25 — when each check is run, and when to re-run it.</t>
+          <t>Document 22, Check Catalog tab — what this check protects against and where it runs.</t>
         </is>
       </c>
     </row>
@@ -1994,50 +1997,62 @@
       </c>
       <c r="B132" s="14" t="inlineStr">
         <is>
+          <t>Document 25 — when each check is run, and when to re-run it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="16" customHeight="1">
+      <c r="A133" s="15" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B133" s="14" t="inlineStr">
+        <is>
           <t>Document 26 — the gate rows this check is ticked against.</t>
         </is>
       </c>
     </row>
-    <row r="133" ht="18" customHeight="1">
-      <c r="B133" s="21" t="inlineStr">
+    <row r="134" ht="18" customHeight="1">
+      <c r="B134" s="21" t="inlineStr">
         <is>
           <t>Work with DAX query view</t>
         </is>
       </c>
     </row>
-    <row r="134" ht="8" customHeight="1"/>
-    <row r="135" ht="22" customHeight="1">
-      <c r="A135" s="5" t="inlineStr">
+    <row r="135" ht="8" customHeight="1"/>
+    <row r="136" ht="22" customHeight="1">
+      <c r="A136" s="5" t="inlineStr">
         <is>
           <t>10. AI ASSISTANCE DISCLOSURE</t>
         </is>
       </c>
     </row>
-    <row r="136" ht="29" customHeight="1">
-      <c r="B136" s="14" t="inlineStr">
+    <row r="137" ht="29" customHeight="1">
+      <c r="B137" s="14" t="inlineStr">
         <is>
           <t>Portions of this procedure were drafted with the assistance of a generative AI system. The author defined the project and its validation approach and reviewed all content before publication.</t>
         </is>
       </c>
     </row>
-    <row r="137" ht="43.5" customHeight="1">
-      <c r="B137" s="14" t="inlineStr">
+    <row r="138" ht="43.5" customHeight="1">
+      <c r="B138" s="14" t="inlineStr">
         <is>
           <t>The pass criterion is quoted from document 02 §9. Queries use only tables, columns and measures defined in documents 02 and 20, and the visual numbers come from the document 15 specification tables. Tool steps were checked against Microsoft Learn; where a screen label varies by version, the procedure says so.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="131">
-    <mergeCell ref="B129:F129"/>
+  <mergeCells count="132">
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="B81:F81"/>
     <mergeCell ref="E111:F111"/>
+    <mergeCell ref="B122:F122"/>
+    <mergeCell ref="B131:F131"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="B131:F131"/>
     <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B52:F52"/>
     <mergeCell ref="C73:D73"/>
-    <mergeCell ref="B52:F52"/>
     <mergeCell ref="C13:F13"/>
     <mergeCell ref="E73:F73"/>
     <mergeCell ref="B42:F42"/>
@@ -2046,118 +2061,119 @@
     <mergeCell ref="C15:F15"/>
     <mergeCell ref="C24:F24"/>
     <mergeCell ref="C116:F116"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B44:F44"/>
     <mergeCell ref="A38:F38"/>
-    <mergeCell ref="B44:F44"/>
-    <mergeCell ref="B53:F53"/>
     <mergeCell ref="C64:F64"/>
     <mergeCell ref="B34:F34"/>
     <mergeCell ref="C26:F26"/>
     <mergeCell ref="A31:F31"/>
-    <mergeCell ref="B108:F108"/>
     <mergeCell ref="C63:F63"/>
     <mergeCell ref="C10:F10"/>
     <mergeCell ref="C93:F93"/>
-    <mergeCell ref="A107:F107"/>
+    <mergeCell ref="B133:F133"/>
+    <mergeCell ref="C105:F105"/>
     <mergeCell ref="B20:F20"/>
-    <mergeCell ref="C105:F105"/>
-    <mergeCell ref="B133:F133"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B94:F94"/>
     <mergeCell ref="E75:F75"/>
-    <mergeCell ref="B94:F94"/>
     <mergeCell ref="C111:D111"/>
     <mergeCell ref="C27:F27"/>
+    <mergeCell ref="A124:F124"/>
+    <mergeCell ref="A108:F108"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B125:F125"/>
     <mergeCell ref="B72:F72"/>
+    <mergeCell ref="B134:F134"/>
     <mergeCell ref="B121:F121"/>
     <mergeCell ref="B56:F56"/>
     <mergeCell ref="C28:F28"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="B43:F43"/>
-    <mergeCell ref="C109:D109"/>
     <mergeCell ref="C96:F96"/>
     <mergeCell ref="C83:F83"/>
     <mergeCell ref="B120:F120"/>
     <mergeCell ref="C92:F92"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="A135:F135"/>
     <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B88:F88"/>
+    <mergeCell ref="B57:F57"/>
     <mergeCell ref="C14:F14"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B88:F88"/>
     <mergeCell ref="B99:F99"/>
     <mergeCell ref="C110:D110"/>
     <mergeCell ref="E110:F110"/>
     <mergeCell ref="B68:F68"/>
-    <mergeCell ref="B124:F124"/>
     <mergeCell ref="C90:F90"/>
     <mergeCell ref="B76:F76"/>
     <mergeCell ref="B45:F45"/>
     <mergeCell ref="B126:F126"/>
+    <mergeCell ref="B109:F109"/>
+    <mergeCell ref="C119:F119"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="C8:F8"/>
     <mergeCell ref="C91:F91"/>
+    <mergeCell ref="A136:F136"/>
     <mergeCell ref="C82:F82"/>
     <mergeCell ref="B46:F46"/>
     <mergeCell ref="A71:F71"/>
+    <mergeCell ref="A129:F129"/>
     <mergeCell ref="C102:F102"/>
     <mergeCell ref="B39:F39"/>
+    <mergeCell ref="C112:D112"/>
     <mergeCell ref="B48:F48"/>
-    <mergeCell ref="B136:F136"/>
     <mergeCell ref="C75:D75"/>
     <mergeCell ref="C97:F97"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="C29:F29"/>
     <mergeCell ref="B137:F137"/>
     <mergeCell ref="C84:F84"/>
+    <mergeCell ref="B65:F65"/>
     <mergeCell ref="C22:F22"/>
-    <mergeCell ref="B65:F65"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="E112:F112"/>
     <mergeCell ref="C12:F12"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="C21:F21"/>
-    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="C95:F95"/>
     <mergeCell ref="B36:F36"/>
-    <mergeCell ref="C95:F95"/>
     <mergeCell ref="A78:F78"/>
     <mergeCell ref="B50:F50"/>
+    <mergeCell ref="B138:F138"/>
     <mergeCell ref="B113:F113"/>
     <mergeCell ref="C23:F23"/>
-    <mergeCell ref="A128:F128"/>
     <mergeCell ref="B100:F100"/>
+    <mergeCell ref="C106:F106"/>
     <mergeCell ref="B66:F66"/>
     <mergeCell ref="C7:F7"/>
     <mergeCell ref="C74:D74"/>
+    <mergeCell ref="B115:F115"/>
     <mergeCell ref="B130:F130"/>
     <mergeCell ref="B86:F86"/>
     <mergeCell ref="B67:F67"/>
     <mergeCell ref="B61:F61"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="A4:F4"/>
-    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B132:F132"/>
     <mergeCell ref="C104:F104"/>
-    <mergeCell ref="B132:F132"/>
     <mergeCell ref="E74:F74"/>
-    <mergeCell ref="B119:F119"/>
     <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B112:F112"/>
+    <mergeCell ref="C103:F103"/>
+    <mergeCell ref="C117:F117"/>
+    <mergeCell ref="B127:F127"/>
     <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C103:F103"/>
     <mergeCell ref="C85:F85"/>
-    <mergeCell ref="C117:F117"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B49:F49"/>
     <mergeCell ref="C9:F9"/>
     <mergeCell ref="C118:F118"/>
     <mergeCell ref="B55:F55"/>
-    <mergeCell ref="A123:F123"/>
     <mergeCell ref="B33:F33"/>
     <mergeCell ref="B89:F89"/>
     <mergeCell ref="B51:F51"/>
     <mergeCell ref="A6:F6"/>
-    <mergeCell ref="C115:F115"/>
     <mergeCell ref="B79:F79"/>
     <mergeCell ref="C11:F11"/>
     <mergeCell ref="B32:F32"/>
-    <mergeCell ref="E109:F109"/>
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B35:F35"/>
   </mergeCells>
